--- a/Book20.xlsx
+++ b/Book20.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5BC6AE0-5235-4F07-BACC-AF422CE46A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tejas.rai\OneDrive - Adventz Group\Desktop\Projects\NISM\NISM-Compliance-Portal\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C968A6E3-C7CD-47A1-B1E2-61B7C7CE555E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D4A67420-F9A9-4758-8D86-7F3E137AF64C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4A67420-F9A9-4758-8D86-7F3E137AF64C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="465">
   <si>
     <t>Employee Number</t>
   </si>
@@ -1415,13 +1420,25 @@
   </si>
   <si>
     <t>Secretarial</t>
+  </si>
+  <si>
+    <t>ZIL001</t>
+  </si>
+  <si>
+    <t>Tejas Rai</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>tejas.rai@adventz.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1441,6 +1458,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1450,7 +1475,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1473,11 +1498,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1488,11 +1525,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1825,23 +1869,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{111B2A5C-0BFA-4346-BAB2-A01E95AFAC65}">
-  <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>443</v>
       </c>
@@ -1876,7 +1920,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1911,7 +1955,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1946,7 +1990,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1981,7 +2025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2016,7 +2060,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2051,7 +2095,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2086,7 +2130,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2121,7 +2165,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2156,7 +2200,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2191,7 +2235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2226,7 +2270,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2261,7 +2305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2296,7 +2340,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2331,7 +2375,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2366,7 +2410,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2401,7 +2445,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2436,7 +2480,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2471,7 +2515,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2506,7 +2550,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2541,7 +2585,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2576,7 +2620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2611,7 +2655,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2646,7 +2690,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2681,7 +2725,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2716,7 +2760,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2751,7 +2795,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2786,7 +2830,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2821,7 +2865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2856,7 +2900,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2891,7 +2935,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2926,7 +2970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2961,7 +3005,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2996,7 +3040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -3031,7 +3075,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -3066,7 +3110,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -3101,7 +3145,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -3136,7 +3180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -3171,7 +3215,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -3204,7 +3248,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -3239,7 +3283,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -3274,7 +3318,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -3309,7 +3353,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -3344,7 +3388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -3379,7 +3423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -3414,7 +3458,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -3449,7 +3493,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3484,7 +3528,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3519,7 +3563,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3554,7 +3598,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3589,7 +3633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3624,7 +3668,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3659,7 +3703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3694,7 +3738,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3729,7 +3773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3764,7 +3808,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3799,7 +3843,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3834,7 +3878,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3869,7 +3913,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3904,7 +3948,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3939,7 +3983,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3974,7 +4018,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -4009,7 +4053,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -4044,7 +4088,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -4079,7 +4123,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -4114,7 +4158,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -4149,7 +4193,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -4184,7 +4228,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -4217,7 +4261,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -4250,7 +4294,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -4285,7 +4329,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -4320,7 +4364,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -4355,7 +4399,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -4390,7 +4434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -4425,7 +4469,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -4460,7 +4504,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -4495,7 +4539,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -4530,7 +4574,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -4565,7 +4609,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -4600,7 +4644,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4635,7 +4679,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -4670,7 +4714,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4705,7 +4749,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -4740,7 +4784,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -4775,7 +4819,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -4810,7 +4854,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4845,7 +4889,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -4880,7 +4924,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4915,7 +4959,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -4950,7 +4994,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4985,7 +5029,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -5020,7 +5064,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -5055,7 +5099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -5090,7 +5134,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -5125,7 +5169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -5160,7 +5204,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -5195,7 +5239,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -5230,7 +5274,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -5265,7 +5309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -5300,7 +5344,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -5335,8 +5379,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A101" s="4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -5351,7 +5395,7 @@
       <c r="E101" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" s="2" t="s">
         <v>227</v>
       </c>
       <c r="G101" s="2" t="s">
@@ -5366,13 +5410,50 @@
       <c r="J101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K101" s="4" t="s">
+      <c r="K101" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="H102">
+        <v>8700986892</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G101" r:id="rId1" display="mailto:HoneyM@adventz.com" xr:uid="{FEC4E2CE-C56D-4F0B-96E1-05A1CDC79ECE}"/>
+    <hyperlink ref="G102" r:id="rId2" xr:uid="{CFD5F205-3B03-44E2-880E-FFA70052BB38}"/>
+    <hyperlink ref="I102" r:id="rId3" xr:uid="{0D140BC8-73C0-4A0D-BBE2-EB39DE152A8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5381,7 +5462,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AAE079-6EC3-4AB3-9781-864E2DE493AA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
